--- a/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-701_CALIFICADO.xlsx
@@ -6614,11 +6614,7 @@
           <t>JUAN SEBASTIAN PEREZ PIEDRAHITA</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1023008561</t>
-        </is>
-      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="n">
         <v>7</v>
       </c>
@@ -6867,11 +6863,7 @@
           <t>JUAN SEBASTIAN PEREZ PIEDRAHITA</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1023008561</t>
-        </is>
-      </c>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="n">
         <v>7</v>
       </c>

--- a/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2245,11 +2221,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2257,7 +2229,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2498,11 +2470,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2510,7 +2478,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2751,11 +2719,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2763,7 +2727,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3000,11 +2964,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3012,7 +2972,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3253,11 +3213,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3265,7 +3221,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3506,11 +3462,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3518,7 +3470,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3759,11 +3711,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3771,7 +3719,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4012,11 +3960,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4024,7 +3968,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4265,11 +4209,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4277,7 +4217,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4518,11 +4458,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4530,7 +4466,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4771,11 +4707,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4783,7 +4715,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5024,11 +4956,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5036,7 +4964,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5277,11 +5205,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5289,7 +5213,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5530,11 +5454,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5542,7 +5462,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5779,11 +5699,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5791,7 +5707,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6032,11 +5948,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6044,7 +5956,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6285,11 +6197,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6297,7 +6205,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6514,11 +6422,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6526,7 +6430,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6767,11 +6671,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6779,7 +6679,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7016,11 +6916,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7028,7 +6924,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7265,11 +7161,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7277,7 +7169,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7510,11 +7402,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7522,7 +7410,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7739,11 +7627,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7751,7 +7635,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -7992,11 +7876,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -8004,7 +7884,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8245,11 +8125,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -8257,7 +8133,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8498,11 +8374,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -8510,7 +8382,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8751,11 +8623,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -8763,7 +8631,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9004,11 +8872,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -9016,7 +8880,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9257,11 +9121,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -9269,7 +9129,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9510,11 +9370,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -9522,7 +9378,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9763,11 +9619,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -9775,7 +9627,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10016,11 +9868,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -10028,7 +9876,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10269,11 +10117,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -10281,7 +10125,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10522,11 +10366,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -10534,7 +10374,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10775,11 +10615,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -10787,7 +10623,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11028,11 +10864,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -11040,7 +10872,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11281,11 +11113,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -11293,7 +11121,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11530,11 +11358,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -11542,7 +11366,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11779,11 +11603,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -11791,7 +11611,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12032,11 +11852,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -12044,7 +11860,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12285,11 +12101,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -12297,7 +12109,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12538,11 +12350,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -12550,7 +12358,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12791,11 +12599,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -12803,7 +12607,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13044,11 +12848,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -13056,7 +12856,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13297,11 +13097,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -13309,7 +13105,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13550,11 +13346,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -13562,7 +13354,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13803,11 +13595,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -13815,7 +13603,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14056,11 +13844,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -14068,7 +13852,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14289,11 +14073,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -14301,7 +14081,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14542,11 +14322,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -14554,7 +14330,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
